--- a/agent_runs/manjidiwang/episodes/ep30/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep30/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>接掌集团（，总时长：10秒，镜头数：3个）</t>
+          <t>接掌集团</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>项目任命（，总时长：10秒，镜头数：4个）</t>
+          <t>项目任命</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>立规警告（，总时长：10秒，镜头数：4个）</t>
+          <t>立规警告</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>阳光运行（，总时长：12秒，镜头数：4个）</t>
+          <t>阳光运行</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>夜色举杯（，总时长：10秒，镜头数：5个）</t>
+          <t>夜色举杯</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>本家来电（，总时长：10秒，镜头数：3个）</t>
+          <t>本家来电</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
